--- a/public/templates/plantilla_docentes.xlsx
+++ b/public/templates/plantilla_docentes.xlsx
@@ -1,41 +1,551 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeanp\Documents\registro\public\templates\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B540998-3CB3-4BD4-B3B6-5431BD5C2F7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Usuarios" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="173">
+  <si>
+    <t>Nombre Completo</t>
+  </si>
+  <si>
+    <t>DNI</t>
+  </si>
+  <si>
+    <t>Rol</t>
+  </si>
+  <si>
+    <t>Sede (Opcional)</t>
+  </si>
+  <si>
+    <t>DOCENTE</t>
+  </si>
+  <si>
+    <t>Campus Villa</t>
+  </si>
+  <si>
+    <t>AGUIRRE ALVAREZ KARINA</t>
+  </si>
+  <si>
+    <t>ALIAGA CASTAÑEDA, WALTER MIJAIL</t>
+  </si>
+  <si>
+    <t>ALIAGA DEL CASTILLO, GABRIELA</t>
+  </si>
+  <si>
+    <t>ALVARADO ZELADA, JACKELYNE JANETH</t>
+  </si>
+  <si>
+    <t>ANICAMA MENDOZA, KARENT LILIANA</t>
+  </si>
+  <si>
+    <t>AQUINO CABRERA, NOEMI</t>
+  </si>
+  <si>
+    <t>ARELLANO RODRIGUEZ, RONAL HAROL</t>
+  </si>
+  <si>
+    <t>ARO GUARDIA, PEDRO ALBERTO</t>
+  </si>
+  <si>
+    <t>ARRIARAN ARONÉS, LIZBETH</t>
+  </si>
+  <si>
+    <t>Arroyo Toscano, Carlix</t>
+  </si>
+  <si>
+    <t>ASENCIO JIMENEZ, HEYSON PIERRE</t>
+  </si>
+  <si>
+    <t>ASTOCAZA FLORES, PERCY ALBERTO</t>
+  </si>
+  <si>
+    <t>Auccacusi Pachari, Erick</t>
+  </si>
+  <si>
+    <t>BARAHONA HERNANDEZ ELMER AMET</t>
+  </si>
+  <si>
+    <t>BARZOLA BUENO, LESLIE ISABEL</t>
+  </si>
+  <si>
+    <t>BERNAOLA MIRANDA, ELVIA HILDA JULIA</t>
+  </si>
+  <si>
+    <t>BORJA VÁSQUEZ, RICHARD</t>
+  </si>
+  <si>
+    <t>Bustamante Bravo Saida Judith</t>
+  </si>
+  <si>
+    <t>Bustamante Quintana,Luis Dhabit Abdel</t>
+  </si>
+  <si>
+    <t>Cardenas Arana, Fernando Luis</t>
+  </si>
+  <si>
+    <t>CARDENAS VENTURO, NICOLAS ALBERTO</t>
+  </si>
+  <si>
+    <t>Carrillo diestra, Gabriela Alexandra</t>
+  </si>
+  <si>
+    <t>CASTILLO CASIANO, FIDEL CARLOS</t>
+  </si>
+  <si>
+    <t>CASTRO ARREDONDO, DAYANNA STEFANY</t>
+  </si>
+  <si>
+    <t>CASTRO CUBAS, RICARDO RAFAEL</t>
+  </si>
+  <si>
+    <t>CASTROMONTE MENACHO, MONICA GENOVEVA</t>
+  </si>
+  <si>
+    <t>Cedrón Gutiérrez, Susan</t>
+  </si>
+  <si>
+    <t>CERVERA ARIAS, KATERINE LISET</t>
+  </si>
+  <si>
+    <t>CHANG CABANILLAS, SERGIO MANUEL</t>
+  </si>
+  <si>
+    <t>CHAVEZ MONTESINOS, Diana Jeanette</t>
+  </si>
+  <si>
+    <t>CHAVEZ PONCE, GLORIA ELSA</t>
+  </si>
+  <si>
+    <t>CHUQUILLANQUI MANRIQUE, YOHANIM YOMO</t>
+  </si>
+  <si>
+    <t>CHUQUITAIPE PACHARI, DAMARIS</t>
+  </si>
+  <si>
+    <t>GUEVARRA CHICOMA, CLOTY</t>
+  </si>
+  <si>
+    <t>CONTRERAS GIL DE ZÚÑIGA, FRESSY MILENY</t>
+  </si>
+  <si>
+    <t>CORREA JURO, OLENKA DANIELA</t>
+  </si>
+  <si>
+    <t>CUADRA MINCHAN,KAREN SOPHIA</t>
+  </si>
+  <si>
+    <t>DAVILA EDQUEN, YOJANA ELIZABETH</t>
+  </si>
+  <si>
+    <t>DEL SOLAR PACHECO, VANNYA DENISSE</t>
+  </si>
+  <si>
+    <t>DIAZ HUATAY, ALEXANDER</t>
+  </si>
+  <si>
+    <t>DONGO OCAMPO WILLIAM</t>
+  </si>
+  <si>
+    <t>ESPICHAN GAMBIRAZIO, ANDREA EUSEBIA</t>
+  </si>
+  <si>
+    <t>FANG MARINO, ALFREDO RENATO</t>
+  </si>
+  <si>
+    <t>FERNANDEZ GRADOS, JUAN MIGUEL</t>
+  </si>
+  <si>
+    <t>FERNÁNDEZ LÓPEZ ELIANA ROSEMARIE</t>
+  </si>
+  <si>
+    <t>FLORES CASTILLO, MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>FLORES LIMAS, JAIME ALBERTO MARTIN</t>
+  </si>
+  <si>
+    <t>FLORES ONOFRE, MANUEL RUBEN</t>
+  </si>
+  <si>
+    <t>FRIBOURG LIENDO, RODRIGO ALONSO</t>
+  </si>
+  <si>
+    <t>GALVEZ VILCHEZ ANAHI</t>
+  </si>
+  <si>
+    <t>GARCÍA CAJALEÓN, JUDITH DAYSI</t>
+  </si>
+  <si>
+    <t>GARCIA LOPEZ, MARIANA LUCIA</t>
+  </si>
+  <si>
+    <t>GARCIA MARTINEZ, DIANA CAROLINA</t>
+  </si>
+  <si>
+    <t>GARCIA VILLAVICENCIO, LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>Garcia Villavicencio,Luis Enrique</t>
+  </si>
+  <si>
+    <t>GONZALEZ CARRILLO, MARY ALEJANDRA</t>
+  </si>
+  <si>
+    <t>GUERRERO RODAS,</t>
+  </si>
+  <si>
+    <t>GUEVARA CHICOMA, CLOTY MARGARI</t>
+  </si>
+  <si>
+    <t>GUEVARA LAZO, PEDRO ARTURO</t>
+  </si>
+  <si>
+    <t>HERRERA SANTOS, GERSOM</t>
+  </si>
+  <si>
+    <t>HINOJOSA OBANDO, MAYDA</t>
+  </si>
+  <si>
+    <t>HUERTA LINARES, SOLEDAD</t>
+  </si>
+  <si>
+    <t>HUAMANI SALAS, CECILIA ELIZABETH</t>
+  </si>
+  <si>
+    <t>INFANTE LINARES, DEBORA ARACELI</t>
+  </si>
+  <si>
+    <t>JACINTO GOMERO, PATRICK JOSÉ</t>
+  </si>
+  <si>
+    <t>Jordan Blancas, Catherina Jesús</t>
+  </si>
+  <si>
+    <t>LABRIN BURGA, JOSSELYN DEL CARMEN</t>
+  </si>
+  <si>
+    <t>LARA SILVA, MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>LAYME PACHECO, GRISSEL JULIA</t>
+  </si>
+  <si>
+    <t>Leon Soto, Janet Olinda</t>
+  </si>
+  <si>
+    <t>LIZARZABURU ROMERO ANGELA PAMELA</t>
+  </si>
+  <si>
+    <t>LLANOS CAMPOS, RENATA</t>
+  </si>
+  <si>
+    <t>MALEE RODRIGO MENDOZA</t>
+  </si>
+  <si>
+    <t>MANOSALVA FARFAN, JORGE ANTONIO</t>
+  </si>
+  <si>
+    <t>Marín Dávalos, Renzo Iván</t>
+  </si>
+  <si>
+    <t>MATALLANA PACHECO, JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>MAURICIO ROBLADILLO, JUAN DANIEL</t>
+  </si>
+  <si>
+    <t>MAYO ARPI DIANA ALISSON</t>
+  </si>
+  <si>
+    <t>MEDINA MOLINA PAOLA</t>
+  </si>
+  <si>
+    <t>MEDINA, MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>Mendoza Anccana Jorge Luis</t>
+  </si>
+  <si>
+    <t>MERINO TABOADA, ANA LUCIA</t>
+  </si>
+  <si>
+    <t>Merino Taboada, Andrea Sofía</t>
+  </si>
+  <si>
+    <t>MERINO ZAMALLOA, YENIFFER</t>
+  </si>
+  <si>
+    <t>Meza Medina, Patricia Verónica</t>
+  </si>
+  <si>
+    <t>MIRAVAL LEÓN, LUBEN JORGE</t>
+  </si>
+  <si>
+    <t>MORALES ROBALINO JESSIE</t>
+  </si>
+  <si>
+    <t>MORALES ZAVALETA, MARTIN OSWALDO</t>
+  </si>
+  <si>
+    <t>MUÑOA CARCAMO, KARLA KIMBERLY</t>
+  </si>
+  <si>
+    <t>NEYRA SOTELO, MANUEL GONZALO</t>
+  </si>
+  <si>
+    <t>OCHOA VICENTE, ROXANA LIZETH</t>
+  </si>
+  <si>
+    <t>OLIVERA SAFORA KELLY</t>
+  </si>
+  <si>
+    <t>ONTANEDA GONZÁLEZ, CLAUDIA LILIANA</t>
+  </si>
+  <si>
+    <t>ORELLANA PRESENTACION , MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>ORTA FLORES, FRANCIS MILAGROS</t>
+  </si>
+  <si>
+    <t>Ortiz Peceros ,José</t>
+  </si>
+  <si>
+    <t>PACO CASTILLO,DALIA NATHALY</t>
+  </si>
+  <si>
+    <t>PAREDES ESPINOZA, ADRIA PATRICIA DEL PILAR</t>
+  </si>
+  <si>
+    <t>PAUCAR ALFARO,JIMMY DANIEL</t>
+  </si>
+  <si>
+    <t>PAUCAR CISNEROS, LINDA ANGIE</t>
+  </si>
+  <si>
+    <t>Pence Tovar,James Alexander</t>
+  </si>
+  <si>
+    <t>PEÑA MAYORGA, CLAUDIA XIMENA</t>
+  </si>
+  <si>
+    <t>PINILLOS PERALTA, MIA PAULA</t>
+  </si>
+  <si>
+    <t>QUIROZ HORNA, BRUNO FABIAN</t>
+  </si>
+  <si>
+    <t>RAMOS ORTIZ RUBEN ALEX</t>
+  </si>
+  <si>
+    <t>RAMOS SERRANO, DANIELA YECENIA</t>
+  </si>
+  <si>
+    <t>REJAS VARILLAS, NADIA CAROLINA</t>
+  </si>
+  <si>
+    <t>REYES ROEL, JORGE RICARDO</t>
+  </si>
+  <si>
+    <t>RODRIGO MENDOZA MALEE</t>
+  </si>
+  <si>
+    <t>RODRÍGUEZ PONCE, CAMILE ELEONORE</t>
+  </si>
+  <si>
+    <t>ROJAS KLAUER DANIELA PATRICIA</t>
+  </si>
+  <si>
+    <t>Romero Gálvez, Susan Jeammy</t>
+  </si>
+  <si>
+    <t>Roxana del Pilar Chique Zevallos</t>
+  </si>
+  <si>
+    <t>Salas Castillo Patricia Liliana</t>
+  </si>
+  <si>
+    <t>Salas Sinclair, Jorge Alfredo</t>
+  </si>
+  <si>
+    <t>Saldaña Cabanillas, David samuel</t>
+  </si>
+  <si>
+    <t>SALDAÑA GASTULO,JIOVANY JHAN CARLOS</t>
+  </si>
+  <si>
+    <t>SALDARRIAGA LECAROS ,CLAUDIA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>SAMANEZ OBESO, ANGEL FRANCISCO</t>
+  </si>
+  <si>
+    <t>SAMANIEGO LARA, DANIELA ELISA</t>
+  </si>
+  <si>
+    <t>SANCHEZ ALARCON, SANDRA SIMONE</t>
+  </si>
+  <si>
+    <t>SILVA MORE, JANET DEL PILAR</t>
+  </si>
+  <si>
+    <t>Silva Rodriguez, Varyn Adriana</t>
+  </si>
+  <si>
+    <t>SINCLAIR REJAS, PATRICIA VICTORIA</t>
+  </si>
+  <si>
+    <t>Suarez Odar, Rosella Yvette</t>
+  </si>
+  <si>
+    <t>TAMBINI MONGE, CLAUDIA GISELLA</t>
+  </si>
+  <si>
+    <t>TARABAY BARRIGA, ANA PATRICIA PIERINA</t>
+  </si>
+  <si>
+    <t>TEJADA PACHECO, CINTHYA GIANINNA</t>
+  </si>
+  <si>
+    <t>TORRES ITURRIZAGA, CINTHYA ROSARIO</t>
+  </si>
+  <si>
+    <t>VALDEZ QUISPE, MICHEL WILFREDO</t>
+  </si>
+  <si>
+    <t>Vallejos Vallo, Maria Fernanda</t>
+  </si>
+  <si>
+    <t>VARGAS SILVA, ELMER ANTONIO</t>
+  </si>
+  <si>
+    <t>VARGAS TORRES YOUNG, DIEGO ALONSO</t>
+  </si>
+  <si>
+    <t>Vásquez de la Cruz, percy tomas</t>
+  </si>
+  <si>
+    <t>VEGAS ZEVALLOS, Juan Francisco</t>
+  </si>
+  <si>
+    <t>VERA MENDEZ, YORJEAN</t>
+  </si>
+  <si>
+    <t>VERA PÉREZ, RICHARD ANDREE</t>
+  </si>
+  <si>
+    <t>VERÁSTEGUI RAMOS, ABEL REYNALDO</t>
+  </si>
+  <si>
+    <t>Villafani Tasayco, Guisella Karina</t>
+  </si>
+  <si>
+    <t>VILLALOBOS LINARES, RENZO RENATO</t>
+  </si>
+  <si>
+    <t>VILLAVICENCIO ESCUDERO TATIANA VANESSA</t>
+  </si>
+  <si>
+    <t>ZÚÑIGA ESCALANTE MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>JOSHIMAR QUISPE GUERRERO</t>
+  </si>
+  <si>
+    <t>RODAS UTANI GROVER</t>
+  </si>
+  <si>
+    <t>GARY SAAVEDRA VILCHEZ</t>
+  </si>
+  <si>
+    <t>Ingrid Pamela Villafuerte Mesco</t>
+  </si>
+  <si>
+    <t>John Emanuel Vasquez Grande</t>
+  </si>
+  <si>
+    <t>EDDY GROBERT CARIAPAZA PALOMINO</t>
+  </si>
+  <si>
+    <t>MIRIAM PAJUELO MENDOZA</t>
+  </si>
+  <si>
+    <t>INGRID CANO SANTOS</t>
+  </si>
+  <si>
+    <t>PIERINA ASTRID PAREDES GONZALES</t>
+  </si>
+  <si>
+    <t>NILA IRIS ANGELES SANCHEZ</t>
+  </si>
+  <si>
+    <t>MAURICIO ALBERTO ARMAS BEST</t>
+  </si>
+  <si>
+    <t>06794536</t>
+  </si>
+  <si>
+    <t>09972679</t>
+  </si>
+  <si>
+    <t>09797102</t>
+  </si>
+  <si>
+    <t>08632350</t>
+  </si>
+  <si>
+    <t>07698383</t>
+  </si>
+  <si>
+    <t>07764687</t>
+  </si>
+  <si>
+    <t>02433237</t>
+  </si>
+  <si>
+    <t>06754202</t>
+  </si>
+  <si>
+    <t>07969482</t>
+  </si>
+  <si>
+    <t>09929465</t>
+  </si>
+  <si>
+    <t>06815009</t>
+  </si>
+  <si>
+    <t>09848752</t>
+  </si>
+  <si>
+    <t>08272573</t>
+  </si>
+  <si>
+    <t>07644677</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -43,16 +553,70 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1E293B"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1E293B"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF242424"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -60,18 +624,146 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="16">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,54 +1088,2176 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D155"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="41.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.8984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.09765625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Nombre Completo</v>
-      </c>
-      <c r="B1" t="str">
-        <v>DNI</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Rol</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Sede (Opcional)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Ejemplo Nombre 1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>11111111</v>
-      </c>
-      <c r="C2" t="str">
-        <v>DOCENTE</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Campus Villa</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Ejemplo Nombre 2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>22222222</v>
-      </c>
-      <c r="C3" t="str">
-        <v>DOCENTE</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Campus Norte</v>
-      </c>
-    </row>
+    <row r="1" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2">
+        <v>70365967</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2">
+        <v>45332462</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2">
+        <v>46443851</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2">
+        <v>46236438</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2">
+        <v>44626392</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="2">
+        <v>42515367</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="2">
+        <v>40000822</v>
+      </c>
+      <c r="C9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="2">
+        <v>40731246</v>
+      </c>
+      <c r="C10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="2">
+        <v>43437721</v>
+      </c>
+      <c r="C11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="2">
+        <v>73239480</v>
+      </c>
+      <c r="C12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="2">
+        <v>45797458</v>
+      </c>
+      <c r="C13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="2">
+        <v>43921049</v>
+      </c>
+      <c r="C14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="2">
+        <v>43795600</v>
+      </c>
+      <c r="C15" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="2">
+        <v>44148827</v>
+      </c>
+      <c r="C16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="2">
+        <v>44108174</v>
+      </c>
+      <c r="C17" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="C18" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="2">
+        <v>46100939</v>
+      </c>
+      <c r="C19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="2">
+        <v>70436697</v>
+      </c>
+      <c r="C20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="2">
+        <v>42036009</v>
+      </c>
+      <c r="C21" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="2">
+        <v>40826435</v>
+      </c>
+      <c r="C22" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="2">
+        <v>74311875</v>
+      </c>
+      <c r="C23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="2">
+        <v>10401241</v>
+      </c>
+      <c r="C24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="2">
+        <v>74208127</v>
+      </c>
+      <c r="C25" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="2">
+        <v>16748560</v>
+      </c>
+      <c r="C26" t="s">
+        <v>4</v>
+      </c>
+      <c r="D26" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="C27" t="s">
+        <v>4</v>
+      </c>
+      <c r="D27" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="2">
+        <v>16733246</v>
+      </c>
+      <c r="C28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D28" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" s="2">
+        <v>74049382</v>
+      </c>
+      <c r="C29" t="s">
+        <v>4</v>
+      </c>
+      <c r="D29" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="2">
+        <v>71104209</v>
+      </c>
+      <c r="C30" t="s">
+        <v>4</v>
+      </c>
+      <c r="D30" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="2">
+        <v>47119775</v>
+      </c>
+      <c r="C31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D31" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="C32" t="s">
+        <v>4</v>
+      </c>
+      <c r="D32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="2">
+        <v>47822782</v>
+      </c>
+      <c r="C33" t="s">
+        <v>4</v>
+      </c>
+      <c r="D33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="2">
+        <v>41271926</v>
+      </c>
+      <c r="C34" t="s">
+        <v>4</v>
+      </c>
+      <c r="D34" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="2">
+        <v>16788147</v>
+      </c>
+      <c r="C35" t="s">
+        <v>4</v>
+      </c>
+      <c r="D35" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="2">
+        <v>46674427</v>
+      </c>
+      <c r="C36" t="s">
+        <v>4</v>
+      </c>
+      <c r="D36" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" s="2">
+        <v>71755422</v>
+      </c>
+      <c r="C37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D37" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" s="2">
+        <v>71853054</v>
+      </c>
+      <c r="C38" t="s">
+        <v>4</v>
+      </c>
+      <c r="D38" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" s="2">
+        <v>16748139</v>
+      </c>
+      <c r="C39" t="s">
+        <v>4</v>
+      </c>
+      <c r="D39" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" s="2">
+        <v>42550653</v>
+      </c>
+      <c r="C40" t="s">
+        <v>4</v>
+      </c>
+      <c r="D40" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" s="2">
+        <v>72882045</v>
+      </c>
+      <c r="C41" t="s">
+        <v>4</v>
+      </c>
+      <c r="D41" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B42" s="2">
+        <v>43269648</v>
+      </c>
+      <c r="C42" t="s">
+        <v>4</v>
+      </c>
+      <c r="D42" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="C43" t="s">
+        <v>4</v>
+      </c>
+      <c r="D43" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B44" s="2">
+        <v>18168014</v>
+      </c>
+      <c r="C44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D44" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" s="2">
+        <v>40767742</v>
+      </c>
+      <c r="C45" t="s">
+        <v>4</v>
+      </c>
+      <c r="D45" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B46" s="2">
+        <v>41589823</v>
+      </c>
+      <c r="C46" t="s">
+        <v>4</v>
+      </c>
+      <c r="D46" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B47" s="2">
+        <v>40318994</v>
+      </c>
+      <c r="C47" t="s">
+        <v>4</v>
+      </c>
+      <c r="D47" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B48" s="7">
+        <v>41638876</v>
+      </c>
+      <c r="C48" t="s">
+        <v>4</v>
+      </c>
+      <c r="D48" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B49" s="2">
+        <v>41220764</v>
+      </c>
+      <c r="C49" t="s">
+        <v>4</v>
+      </c>
+      <c r="D49" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B50" s="2">
+        <v>72930402</v>
+      </c>
+      <c r="C50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D50" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B51" s="2">
+        <v>45035019</v>
+      </c>
+      <c r="C51" t="s">
+        <v>4</v>
+      </c>
+      <c r="D51" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B52" s="2">
+        <v>22486408</v>
+      </c>
+      <c r="C52" t="s">
+        <v>4</v>
+      </c>
+      <c r="D52" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B53" s="2">
+        <v>76234127</v>
+      </c>
+      <c r="C53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D53" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B54" s="2">
+        <v>45072651</v>
+      </c>
+      <c r="C54" t="s">
+        <v>4</v>
+      </c>
+      <c r="D54" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="C55" t="s">
+        <v>4</v>
+      </c>
+      <c r="D55" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B56" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="C56" t="s">
+        <v>4</v>
+      </c>
+      <c r="D56" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="C57" t="s">
+        <v>4</v>
+      </c>
+      <c r="D57" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B58" s="2">
+        <v>41568950</v>
+      </c>
+      <c r="C58" t="s">
+        <v>4</v>
+      </c>
+      <c r="D58" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B59" s="2">
+        <v>16788147</v>
+      </c>
+      <c r="C59" t="s">
+        <v>4</v>
+      </c>
+      <c r="D59" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B60" s="2">
+        <v>46406109</v>
+      </c>
+      <c r="C60" t="s">
+        <v>4</v>
+      </c>
+      <c r="D60" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B61" s="2">
+        <v>41884441</v>
+      </c>
+      <c r="C61" t="s">
+        <v>4</v>
+      </c>
+      <c r="D61" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B62" s="2">
+        <v>29368980</v>
+      </c>
+      <c r="C62" t="s">
+        <v>4</v>
+      </c>
+      <c r="D62" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B63" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="C63" t="s">
+        <v>4</v>
+      </c>
+      <c r="D63" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B64" s="2">
+        <v>29723258</v>
+      </c>
+      <c r="C64" t="s">
+        <v>4</v>
+      </c>
+      <c r="D64" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B65" s="2">
+        <v>18160488</v>
+      </c>
+      <c r="C65" t="s">
+        <v>4</v>
+      </c>
+      <c r="D65" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B66" s="2">
+        <v>45428258</v>
+      </c>
+      <c r="C66" t="s">
+        <v>4</v>
+      </c>
+      <c r="D66" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B67" s="2">
+        <v>21532780</v>
+      </c>
+      <c r="C67" t="s">
+        <v>4</v>
+      </c>
+      <c r="D67" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B68" s="2">
+        <v>45872498</v>
+      </c>
+      <c r="C68" t="s">
+        <v>4</v>
+      </c>
+      <c r="D68" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B69" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="C69" t="s">
+        <v>4</v>
+      </c>
+      <c r="D69" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B70" s="2">
+        <v>44125472</v>
+      </c>
+      <c r="C70" t="s">
+        <v>4</v>
+      </c>
+      <c r="D70" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B71" s="2">
+        <v>40409705</v>
+      </c>
+      <c r="C71" t="s">
+        <v>4</v>
+      </c>
+      <c r="D71" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B72" s="2">
+        <v>42362119</v>
+      </c>
+      <c r="C72" t="s">
+        <v>4</v>
+      </c>
+      <c r="D72" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B73" s="2">
+        <v>74294800</v>
+      </c>
+      <c r="C73" t="s">
+        <v>4</v>
+      </c>
+      <c r="D73" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B74" s="2">
+        <v>42945202</v>
+      </c>
+      <c r="C74" t="s">
+        <v>4</v>
+      </c>
+      <c r="D74" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B75" s="2">
+        <v>42553786</v>
+      </c>
+      <c r="C75" t="s">
+        <v>4</v>
+      </c>
+      <c r="D75" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B76" s="2">
+        <v>43531520</v>
+      </c>
+      <c r="C76" t="s">
+        <v>4</v>
+      </c>
+      <c r="D76" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B77" s="2">
+        <v>70687952</v>
+      </c>
+      <c r="C77" t="s">
+        <v>4</v>
+      </c>
+      <c r="D77" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B78" s="2">
+        <v>40082088</v>
+      </c>
+      <c r="C78" t="s">
+        <v>4</v>
+      </c>
+      <c r="D78" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B79" s="2">
+        <v>74660566</v>
+      </c>
+      <c r="C79" t="s">
+        <v>4</v>
+      </c>
+      <c r="D79" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B80" s="2">
+        <v>72207901</v>
+      </c>
+      <c r="C80" t="s">
+        <v>4</v>
+      </c>
+      <c r="D80" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B81" s="2">
+        <v>72939897</v>
+      </c>
+      <c r="C81" t="s">
+        <v>4</v>
+      </c>
+      <c r="D81" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B82" s="2">
+        <v>80071872</v>
+      </c>
+      <c r="C82" t="s">
+        <v>4</v>
+      </c>
+      <c r="D82" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B83" s="2">
+        <v>45780984</v>
+      </c>
+      <c r="C83" t="s">
+        <v>4</v>
+      </c>
+      <c r="D83" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B84" s="2">
+        <v>41870233</v>
+      </c>
+      <c r="C84" t="s">
+        <v>4</v>
+      </c>
+      <c r="D84" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B85" s="2">
+        <v>43930794</v>
+      </c>
+      <c r="C85" t="s">
+        <v>4</v>
+      </c>
+      <c r="D85" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B86" s="2">
+        <v>43431404</v>
+      </c>
+      <c r="C86" t="s">
+        <v>4</v>
+      </c>
+      <c r="D86" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B87" s="2">
+        <v>44916367</v>
+      </c>
+      <c r="C87" t="s">
+        <v>4</v>
+      </c>
+      <c r="D87" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B88" s="2">
+        <v>40682132</v>
+      </c>
+      <c r="C88" t="s">
+        <v>4</v>
+      </c>
+      <c r="D88" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B89" s="2">
+        <v>44107104</v>
+      </c>
+      <c r="C89" t="s">
+        <v>4</v>
+      </c>
+      <c r="D89" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B90" s="2">
+        <v>44114270</v>
+      </c>
+      <c r="C90" t="s">
+        <v>4</v>
+      </c>
+      <c r="D90" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B91" s="2">
+        <v>21520485</v>
+      </c>
+      <c r="C91" t="s">
+        <v>4</v>
+      </c>
+      <c r="D91" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B92" s="2">
+        <v>43460316</v>
+      </c>
+      <c r="C92" t="s">
+        <v>4</v>
+      </c>
+      <c r="D92" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B93" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="C93" t="s">
+        <v>4</v>
+      </c>
+      <c r="D93" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B94" s="2">
+        <v>25844618</v>
+      </c>
+      <c r="C94" t="s">
+        <v>4</v>
+      </c>
+      <c r="D94" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A95" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B95" s="2">
+        <v>70294355</v>
+      </c>
+      <c r="C95" t="s">
+        <v>4</v>
+      </c>
+      <c r="D95" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B96" s="2">
+        <v>41640396</v>
+      </c>
+      <c r="C96" t="s">
+        <v>4</v>
+      </c>
+      <c r="D96" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B97" s="2">
+        <v>40050579</v>
+      </c>
+      <c r="C97" t="s">
+        <v>4</v>
+      </c>
+      <c r="D97" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B98" s="2">
+        <v>47173480</v>
+      </c>
+      <c r="C98" t="s">
+        <v>4</v>
+      </c>
+      <c r="D98" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B99" s="2">
+        <v>41273390</v>
+      </c>
+      <c r="C99" t="s">
+        <v>4</v>
+      </c>
+      <c r="D99" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A100" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B100" s="2">
+        <v>45590196</v>
+      </c>
+      <c r="C100" t="s">
+        <v>4</v>
+      </c>
+      <c r="D100" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B101" s="2">
+        <v>48479396</v>
+      </c>
+      <c r="C101" t="s">
+        <v>4</v>
+      </c>
+      <c r="D101" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A102" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B102" s="2">
+        <v>73870101</v>
+      </c>
+      <c r="C102" t="s">
+        <v>4</v>
+      </c>
+      <c r="D102" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A103" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B103" s="2">
+        <v>43180392</v>
+      </c>
+      <c r="C103" t="s">
+        <v>4</v>
+      </c>
+      <c r="D103" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B104" s="2">
+        <v>70435987</v>
+      </c>
+      <c r="C104" t="s">
+        <v>4</v>
+      </c>
+      <c r="D104" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A105" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B105" s="2">
+        <v>44240891</v>
+      </c>
+      <c r="C105" t="s">
+        <v>4</v>
+      </c>
+      <c r="D105" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B106" s="2">
+        <v>21539491</v>
+      </c>
+      <c r="C106" t="s">
+        <v>4</v>
+      </c>
+      <c r="D106" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A107" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B107" s="2">
+        <v>40150659</v>
+      </c>
+      <c r="C107" t="s">
+        <v>4</v>
+      </c>
+      <c r="D107" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A108" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B108" s="2">
+        <v>42939834</v>
+      </c>
+      <c r="C108" t="s">
+        <v>4</v>
+      </c>
+      <c r="D108" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A109" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B109" s="2">
+        <v>70754340</v>
+      </c>
+      <c r="C109" t="s">
+        <v>4</v>
+      </c>
+      <c r="D109" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A110" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B110" s="2">
+        <v>42945202</v>
+      </c>
+      <c r="C110" t="s">
+        <v>4</v>
+      </c>
+      <c r="D110" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A111" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B111" s="2">
+        <v>41880782</v>
+      </c>
+      <c r="C111" t="s">
+        <v>4</v>
+      </c>
+      <c r="D111" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A112" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B112" s="2">
+        <v>46834224</v>
+      </c>
+      <c r="C112" t="s">
+        <v>4</v>
+      </c>
+      <c r="D112" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A113" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B113" s="2">
+        <v>42018087</v>
+      </c>
+      <c r="C113" t="s">
+        <v>4</v>
+      </c>
+      <c r="D113" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A114" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B114" s="2">
+        <v>45567847</v>
+      </c>
+      <c r="C114" t="s">
+        <v>4</v>
+      </c>
+      <c r="D114" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A115" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B115" s="2">
+        <v>41373589</v>
+      </c>
+      <c r="C115" t="s">
+        <v>4</v>
+      </c>
+      <c r="D115" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A116" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B116" s="2">
+        <v>48949963</v>
+      </c>
+      <c r="C116" t="s">
+        <v>4</v>
+      </c>
+      <c r="D116" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B117" s="2">
+        <v>72721849</v>
+      </c>
+      <c r="C117" t="s">
+        <v>4</v>
+      </c>
+      <c r="D117" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A118" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B118" s="2">
+        <v>45882543</v>
+      </c>
+      <c r="C118" t="s">
+        <v>4</v>
+      </c>
+      <c r="D118" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A119" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B119" s="2">
+        <v>45461907</v>
+      </c>
+      <c r="C119" t="s">
+        <v>4</v>
+      </c>
+      <c r="D119" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A120" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B120" s="2">
+        <v>44296813</v>
+      </c>
+      <c r="C120" t="s">
+        <v>4</v>
+      </c>
+      <c r="D120" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B121" s="2">
+        <v>40517859</v>
+      </c>
+      <c r="C121" t="s">
+        <v>4</v>
+      </c>
+      <c r="D121" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A122" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B122" s="2">
+        <v>40506695</v>
+      </c>
+      <c r="C122" t="s">
+        <v>4</v>
+      </c>
+      <c r="D122" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A123" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B123" s="2">
+        <v>41328847</v>
+      </c>
+      <c r="C123" t="s">
+        <v>4</v>
+      </c>
+      <c r="D123" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A124" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B124" s="2">
+        <v>72750429</v>
+      </c>
+      <c r="C124" t="s">
+        <v>4</v>
+      </c>
+      <c r="D124" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A125" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B125" s="2">
+        <v>45635460</v>
+      </c>
+      <c r="C125" t="s">
+        <v>4</v>
+      </c>
+      <c r="D125" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A126" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B126" s="2">
+        <v>43503558</v>
+      </c>
+      <c r="C126" t="s">
+        <v>4</v>
+      </c>
+      <c r="D126" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A127" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B127" s="2">
+        <v>41803194</v>
+      </c>
+      <c r="C127" t="s">
+        <v>4</v>
+      </c>
+      <c r="D127" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A128" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B128" s="2">
+        <v>72930245</v>
+      </c>
+      <c r="C128" t="s">
+        <v>4</v>
+      </c>
+      <c r="D128" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A129" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B129" s="2">
+        <v>42887445</v>
+      </c>
+      <c r="C129" t="s">
+        <v>4</v>
+      </c>
+      <c r="D129" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A130" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B130" s="2">
+        <v>42744794</v>
+      </c>
+      <c r="C130" t="s">
+        <v>4</v>
+      </c>
+      <c r="D130" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A131" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B131" s="2">
+        <v>47090450</v>
+      </c>
+      <c r="C131" t="s">
+        <v>4</v>
+      </c>
+      <c r="D131" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A132" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B132" s="2">
+        <v>73510800</v>
+      </c>
+      <c r="C132" t="s">
+        <v>4</v>
+      </c>
+      <c r="D132" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A133" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B133" s="2">
+        <v>70051181</v>
+      </c>
+      <c r="C133" t="s">
+        <v>4</v>
+      </c>
+      <c r="D133" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A134" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B134" s="2">
+        <v>71243515</v>
+      </c>
+      <c r="C134" t="s">
+        <v>4</v>
+      </c>
+      <c r="D134" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A135" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B135" s="2">
+        <v>71792424</v>
+      </c>
+      <c r="C135" t="s">
+        <v>4</v>
+      </c>
+      <c r="D135" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A136" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B136" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="C136" t="s">
+        <v>4</v>
+      </c>
+      <c r="D136" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A137" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B137" s="2">
+        <v>47938328</v>
+      </c>
+      <c r="C137" t="s">
+        <v>4</v>
+      </c>
+      <c r="D137" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A138" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B138" s="2">
+        <v>73545651</v>
+      </c>
+      <c r="C138" t="s">
+        <v>4</v>
+      </c>
+      <c r="D138" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A139" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B139" s="2">
+        <v>40161018</v>
+      </c>
+      <c r="C139" t="s">
+        <v>4</v>
+      </c>
+      <c r="D139" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A140" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B140" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="C140" t="s">
+        <v>4</v>
+      </c>
+      <c r="D140" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A141" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B141" s="2">
+        <v>47768598</v>
+      </c>
+      <c r="C141" t="s">
+        <v>4</v>
+      </c>
+      <c r="D141" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A142" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B142" s="2">
+        <v>70437484</v>
+      </c>
+      <c r="C142" t="s">
+        <v>4</v>
+      </c>
+      <c r="D142" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A143" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B143" s="2">
+        <v>44248886</v>
+      </c>
+      <c r="C143" t="s">
+        <v>4</v>
+      </c>
+      <c r="D143" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A144" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="B144" s="2">
+        <v>70426362</v>
+      </c>
+      <c r="C144" t="s">
+        <v>4</v>
+      </c>
+      <c r="D144" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A145" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="B145" s="2">
+        <v>43824266</v>
+      </c>
+      <c r="C145" t="s">
+        <v>4</v>
+      </c>
+      <c r="D145" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A146" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="B146" s="2">
+        <v>75726785</v>
+      </c>
+      <c r="C146" t="s">
+        <v>4</v>
+      </c>
+      <c r="D146" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A147" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="B147" s="2">
+        <v>47480186</v>
+      </c>
+      <c r="C147" t="s">
+        <v>4</v>
+      </c>
+      <c r="D147" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A148" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="B148" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="C148" t="s">
+        <v>4</v>
+      </c>
+      <c r="D148" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A149" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="B149" s="2">
+        <v>29593325</v>
+      </c>
+      <c r="C149" t="s">
+        <v>4</v>
+      </c>
+      <c r="D149" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A150" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="B150" s="2">
+        <v>10728534</v>
+      </c>
+      <c r="C150" t="s">
+        <v>4</v>
+      </c>
+      <c r="D150" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A151" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="B151" s="2">
+        <v>71497836</v>
+      </c>
+      <c r="C151" t="s">
+        <v>4</v>
+      </c>
+      <c r="D151" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A152" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="B152" s="2">
+        <v>46480653</v>
+      </c>
+      <c r="C152" t="s">
+        <v>4</v>
+      </c>
+      <c r="D152" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A153" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="B153" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="C153" t="s">
+        <v>4</v>
+      </c>
+      <c r="D153" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A154" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="B154" s="2">
+        <v>80373084</v>
+      </c>
+      <c r="C154" t="s">
+        <v>4</v>
+      </c>
+      <c r="D154" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" ht="15.6" x14ac:dyDescent="0.3"/>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+    <ignoredError sqref="A1:D1 C2:D2 C3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>